--- a/data/datos_reales/xlsx/DatosReales_CICES_Entidad.xlsx
+++ b/data/datos_reales/xlsx/DatosReales_CICES_Entidad.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\angie\IdeaProjects\cices-system\data\datos_reales\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28E0017D-F1EA-47F3-9069-0BFFC45E635F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F88BCACF-C3C9-4BAC-8505-E61160D91407}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
   <si>
     <t>ID_ENTIDAD</t>
   </si>
@@ -28,30 +28,18 @@
     <t>NOMBRE</t>
   </si>
   <si>
-    <t>PAIS</t>
-  </si>
-  <si>
     <t>ID_CODIGO_TIPO_ENTIDAD</t>
   </si>
   <si>
     <t>Case Western Reserve University</t>
   </si>
   <si>
-    <t>US</t>
-  </si>
-  <si>
     <t>Universidad Hospital Italiano de Buenos Aires</t>
   </si>
   <si>
-    <t>AR</t>
-  </si>
-  <si>
     <t>UCR - Universidad de Costa Rica</t>
   </si>
   <si>
-    <t>CR</t>
-  </si>
-  <si>
     <t>Universidad de Miami</t>
   </si>
   <si>
@@ -61,18 +49,12 @@
     <t>Universidad Rey Juan Carlos</t>
   </si>
   <si>
-    <t>ES</t>
-  </si>
-  <si>
     <t>Universidad Estatal de Florida</t>
   </si>
   <si>
     <t>Universidad Libre de Berlín</t>
   </si>
   <si>
-    <t>DE</t>
-  </si>
-  <si>
     <t>Seminario Bautista de Costa Rica</t>
   </si>
   <si>
@@ -85,18 +67,12 @@
     <t>UNAM – Universidad Nacional Autónoma de México</t>
   </si>
   <si>
-    <t>MX</t>
-  </si>
-  <si>
     <t>Ministerio de Educación de España</t>
   </si>
   <si>
     <t>Universidad de São Paulo</t>
   </si>
   <si>
-    <t>BR</t>
-  </si>
-  <si>
     <t>CONIS – Ministerio de Salud (Costa Rica)</t>
   </si>
   <si>
@@ -127,15 +103,9 @@
     <t>Neuropsicología RD</t>
   </si>
   <si>
-    <t>DO</t>
-  </si>
-  <si>
     <t>Universidad de Borås</t>
   </si>
   <si>
-    <t>SE</t>
-  </si>
-  <si>
     <t>Harvard Graduate School of Education – Universidad de Harvard</t>
   </si>
   <si>
@@ -179,9 +149,6 @@
   </si>
   <si>
     <t xml:space="preserve">Centro Internacional de Entrenamiento en Urgencias &amp; Emergencias - Fundación Salamandra </t>
-  </si>
-  <si>
-    <t>CO</t>
   </si>
   <si>
     <t>UNA - Universidad NacionaL</t>
@@ -475,13 +442,13 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D42"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="4" width="25.77734375" customWidth="1"/>
+    <col min="3" max="3" width="25.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -491,581 +458,455 @@
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="3">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+      <c r="C2" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="3">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+      <c r="C3" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="3">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+      <c r="C4" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D5" s="3">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="C5" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="3">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+      <c r="C6" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="3">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+      <c r="C7" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D8" s="3">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+      <c r="C8" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D9" s="3">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+      <c r="C9" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D10" s="3">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+      <c r="C10" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>10</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11" s="3">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+      <c r="C11" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>11</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D12" s="3">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+      <c r="C12" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
         <v>12</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C13" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D13" s="3">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C13" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D14" s="3">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+      <c r="C14" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <v>14</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D15" s="3">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="C15" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
         <v>15</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D16" s="3">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+      <c r="C16" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
         <v>16</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D17" s="3">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+      <c r="C17" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
         <v>17</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D18" s="3">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+      <c r="C18" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
         <v>18</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D19" s="3">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+      <c r="C19" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
         <v>19</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D20" s="3">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+      <c r="C20" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
         <v>20</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D21" s="3">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="C21" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3">
         <v>21</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D22" s="3">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+      <c r="C22" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3">
         <v>22</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D23" s="3">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>23</v>
+      </c>
+      <c r="C23" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3">
         <v>23</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D24" s="3">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+      <c r="C24" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3">
         <v>24</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D25" s="3">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+      <c r="C25" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3">
         <v>25</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D26" s="3">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+      <c r="C26" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A27" s="3">
         <v>26</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D27" s="3">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
+        <v>27</v>
+      </c>
+      <c r="C27" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A28" s="3">
         <v>27</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D28" s="3">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+      <c r="C28" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A29" s="3">
         <v>28</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D29" s="3">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+      <c r="C29" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A30" s="3">
         <v>29</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D30" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+      <c r="C30" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A31" s="3">
         <v>30</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D31" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+      <c r="C31" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A32" s="3">
         <v>31</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D32" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+      <c r="C32" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A33" s="3">
         <v>32</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D33" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+      <c r="C33" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A34" s="3">
         <v>33</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D34" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+      <c r="C34" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="A35" s="3">
         <v>34</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D35" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+      <c r="C35" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A36" s="3">
         <v>35</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D36" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+        <v>36</v>
+      </c>
+      <c r="C36" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A37" s="3">
         <v>36</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D37" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+        <v>37</v>
+      </c>
+      <c r="C37" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A38" s="3">
         <v>37</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D38" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+        <v>38</v>
+      </c>
+      <c r="C38" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A39" s="3">
         <v>38</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D39" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
+        <v>39</v>
+      </c>
+      <c r="C39" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A40" s="3">
         <v>39</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D40" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+      <c r="C40" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A41" s="3">
         <v>40</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D41" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" ht="124.8" x14ac:dyDescent="0.3">
+        <v>41</v>
+      </c>
+      <c r="C41" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="124.8" x14ac:dyDescent="0.3">
       <c r="A42" s="6">
         <v>41</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="C42" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="D42" s="3">
+        <v>42</v>
+      </c>
+      <c r="C42" s="3">
         <v>27</v>
       </c>
     </row>
